--- a/数据表/Prop.xlsx
+++ b/数据表/Prop.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -46,6 +46,15 @@
     <t>IconAssetName</t>
   </si>
   <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>PriceRandomPercent</t>
+  </si>
+  <si>
     <t>Modifiers</t>
   </si>
   <si>
@@ -55,6 +64,12 @@
     <t>string</t>
   </si>
   <si>
+    <t>RarityType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>StatModifier[]</t>
   </si>
   <si>
@@ -70,34 +85,151 @@
     <t>图标资源名</t>
   </si>
   <si>
+    <t>道具品质</t>
+  </si>
+  <si>
+    <t>道具价格</t>
+  </si>
+  <si>
+    <t>价格浮动</t>
+  </si>
+  <si>
     <t>道具属性</t>
   </si>
   <si>
-    <t>测试道具</t>
-  </si>
-  <si>
-    <t>药</t>
+    <t>道具_1</t>
   </si>
   <si>
     <t>Almighty_Icon</t>
   </si>
   <si>
-    <t>[{"StatType":"MovementSpeed","Value":0.5,"IsPercent":false},{"StatType":"MaxHealth","Value":0.2,"IsPercent":true}]</t>
-  </si>
-  <si>
-    <t>小药</t>
-  </si>
-  <si>
-    <t>中药</t>
-  </si>
-  <si>
-    <t>[{"StatType":"Critical","Value":20,"IsPercent":false},{"StatType":"Defense","Value":1,"IsPercent":false}]</t>
-  </si>
-  <si>
-    <t>大药</t>
-  </si>
-  <si>
-    <t>[{"StatType":"Attack","Value":2,"IsPercent":false},{"StatType":"AttackSpeed","Value":0.1,"IsPercent":true}]</t>
+    <t>White</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":10,"IsPercent":false},{"StatType":"Defense","Value":12,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_2</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":53,"IsPercent":false},{"StatType":"AttackSpeed","Value":0.09,"IsPercent":true},{"StatType":"Attack","Value":11,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_3</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Critical","Value":15,"IsPercent":false},{"StatType":"CriticalDamage","Value":21,"IsPercent":false},{"StatType":"Defense","Value":23,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_4</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Defense","Value":79,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_5</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MovementSpeed","Value":0.8,"IsPercent":false},{"StatType":"Attack","Value":10,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_6</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Dodge","Value":10,"IsPercent":false},{"StatType":"Attack","Value":12,"IsPercent":false},{"StatType":"MaxHealth","Value":44,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_7</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Defense","Value":62,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_8</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":44,"IsPercent":false},{"StatType":"Dodge","Value":27,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_9</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":32,"IsPercent":false},{"StatType":"Attack","Value":7,"IsPercent":false},{"StatType":"Defense","Value":8,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_10</t>
+  </si>
+  <si>
+    <t>[{"StatType":"AttackSpeed","Value":0.19,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>道具_11</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":57,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_12</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":139,"IsPercent":false},{"StatType":"Critical","Value":27,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_13</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Critical","Value":5,"IsPercent":false},{"StatType":"Dodge","Value":7,"IsPercent":false},{"StatType":"MovementSpeed","Value":0.6,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_14</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Defense","Value":38,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_15</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MovementSpeed","Value":1.6,"IsPercent":false},{"StatType":"Defense","Value":32,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_16</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Dodge","Value":28,"IsPercent":false},{"StatType":"Defense","Value":24,"IsPercent":false},{"StatType":"Attack","Value":24,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_17</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Defense","Value":23,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_18</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":17,"IsPercent":false},{"StatType":"MaxHealth","Value":69,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_19</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":74,"IsPercent":false},{"StatType":"Attack","Value":19,"IsPercent":false},{"StatType":"Dodge","Value":20,"IsPercent":false}]</t>
+  </si>
+  <si>
+    <t>道具_20</t>
+  </si>
+  <si>
+    <t>[{"StatType":"AttackSpeed","Value":0.15,"IsPercent":true},{"StatType":"Attack","Value":29,"IsPercent":false},{"StatType":"Defense","Value":27,"IsPercent":false}]</t>
   </si>
 </sst>
 </file>
@@ -718,13 +850,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1037,142 +1169,575 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="10.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="16.4545454545455" customWidth="1"/>
-    <col min="6" max="6" width="50.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="10.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8181818181818" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6363636363636" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.9090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="66.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="42" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" s="1">
         <v>101</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="42" spans="1:6">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1">
+        <v>119</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="42" spans="1:6">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1">
+        <v>225</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.0799999982118607</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" ht="56" spans="1:6">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>329</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8" s="1">
         <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1">
+        <v>423</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.119999997317791</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="1">
+        <v>105</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1">
+        <v>120</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="1">
+        <v>106</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="1">
+        <v>195</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.0799999982118607</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="1">
+        <v>107</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
+        <v>335</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="1">
+        <v>108</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1">
+        <v>433</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.119999997317791</v>
+      </c>
+      <c r="I12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="1">
+        <v>109</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
+        <v>121</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="I13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="1">
+        <v>110</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="1">
+        <v>198</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.0799999982118607</v>
+      </c>
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="1">
+        <v>111</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="1">
+        <v>341</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="1">
+        <v>112</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="1">
+        <v>443</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.119999997317791</v>
+      </c>
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="1">
+        <v>113</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="1">
+        <v>122</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="1">
+        <v>114</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="1">
+        <v>201</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.0799999982118607</v>
+      </c>
+      <c r="I18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="1">
+        <v>115</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>346</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="1">
+        <v>116</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="1">
+        <v>454</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.119999997317791</v>
+      </c>
+      <c r="I20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="1">
+        <v>117</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="1">
+        <v>124</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.0500000007450581</v>
+      </c>
+      <c r="I21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="1">
+        <v>118</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1">
+        <v>204</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.0799999982118607</v>
+      </c>
+      <c r="I22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="1">
+        <v>119</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="1">
+        <v>352</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="1">
+        <v>120</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="1">
+        <v>464</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.119999997317791</v>
+      </c>
+      <c r="I24" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
